--- a/data.xlsx
+++ b/data.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="IP_Data" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
   <si>
     <t>Дата</t>
   </si>
@@ -79,6 +79,75 @@
   </si>
   <si>
     <t>Мария Кузнецова</t>
+  </si>
+  <si>
+    <t>Наименование ТЗ</t>
+  </si>
+  <si>
+    <t>Статус</t>
+  </si>
+  <si>
+    <t>Страна</t>
+  </si>
+  <si>
+    <t>РФ</t>
+  </si>
+  <si>
+    <t>Кузя</t>
+  </si>
+  <si>
+    <t>Регистрация</t>
+  </si>
+  <si>
+    <t>Продление</t>
+  </si>
+  <si>
+    <t>Привет, ромашки</t>
+  </si>
+  <si>
+    <t>Ветер в волосах</t>
+  </si>
+  <si>
+    <t>В работе</t>
+  </si>
+  <si>
+    <t>Казахстан</t>
+  </si>
+  <si>
+    <t>Белый лебедь</t>
+  </si>
+  <si>
+    <t>Долина радости</t>
+  </si>
+  <si>
+    <t>Чили</t>
+  </si>
+  <si>
+    <t>Зомбиленд</t>
+  </si>
+  <si>
+    <t>Эквадор</t>
+  </si>
+  <si>
+    <t>Улыбка</t>
+  </si>
+  <si>
+    <t>Китай</t>
+  </si>
+  <si>
+    <t>снеговик из мороженого</t>
+  </si>
+  <si>
+    <t>Чистый лист</t>
+  </si>
+  <si>
+    <t>Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Номер </t>
+  </si>
+  <si>
+    <t>Дата приоритета</t>
   </si>
 </sst>
 </file>
@@ -114,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +205,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -665,10 +744,231 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="19.6328125" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.08984375" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="8"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2">
+        <v>8746392</v>
+      </c>
+      <c r="C2" s="9">
+        <v>41406</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="9">
+        <v>45058</v>
+      </c>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>7392646</v>
+      </c>
+      <c r="C3" s="9">
+        <v>43292</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="9">
+        <v>46945</v>
+      </c>
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
+        <v>6352419</v>
+      </c>
+      <c r="C4" s="9">
+        <v>46124</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="9">
+        <v>49777</v>
+      </c>
+      <c r="G4" s="9"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5">
+        <v>63535289</v>
+      </c>
+      <c r="C5" s="9">
+        <v>45636</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="9">
+        <v>49288</v>
+      </c>
+      <c r="G5" s="9"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <v>73920</v>
+      </c>
+      <c r="C6" s="9">
+        <v>45055</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="9">
+        <v>48708</v>
+      </c>
+      <c r="G6" s="9"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7">
+        <v>629302</v>
+      </c>
+      <c r="C7" s="9">
+        <v>43748</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="9">
+        <v>47401</v>
+      </c>
+      <c r="G7" s="9"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8">
+        <v>62291544</v>
+      </c>
+      <c r="C8" s="9">
+        <v>43411</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="9">
+        <v>47064</v>
+      </c>
+      <c r="G8" s="9"/>
+    </row>
+    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9">
+        <v>632008</v>
+      </c>
+      <c r="C9" s="9">
+        <v>45368</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="9">
+        <v>49020</v>
+      </c>
+      <c r="G9" s="9"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10">
+        <v>390461</v>
+      </c>
+      <c r="C10" s="9">
+        <v>45780</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="9">
+        <v>49432</v>
+      </c>
+      <c r="G10" s="9"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="договоры" sheetId="1" r:id="rId1"/>
     <sheet name="IP_Data" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>

--- a/data.xlsx
+++ b/data.xlsx
@@ -9,14 +9,13 @@
   <sheets>
     <sheet name="договоры" sheetId="1" r:id="rId1"/>
     <sheet name="IP_Data" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="44">
   <si>
     <t>Дата</t>
   </si>
@@ -517,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" customWidth="1"/>
@@ -733,6 +732,213 @@
         <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="9">
+        <v>45455</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="4">
+        <v>9000000</v>
+      </c>
+      <c r="E10" s="1">
+        <v>7</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="9">
+        <v>45603</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="4">
+        <v>4000000</v>
+      </c>
+      <c r="E11" s="1">
+        <v>8</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="9">
+        <v>45634</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1">
+        <v>6</v>
+      </c>
+      <c r="D12" s="4">
+        <v>5000300</v>
+      </c>
+      <c r="E12" s="1">
+        <v>7</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="9">
+        <v>45032</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1">
+        <v>7</v>
+      </c>
+      <c r="D13" s="4">
+        <v>9000000</v>
+      </c>
+      <c r="E13" s="1">
+        <v>6</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="9">
+        <v>44999</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1">
+        <v>6</v>
+      </c>
+      <c r="D14" s="4">
+        <v>8000000</v>
+      </c>
+      <c r="E14" s="1">
+        <v>5</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="9">
+        <v>45387</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="1">
+        <v>9</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="9">
+        <v>45389</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="1">
+        <v>6</v>
+      </c>
+      <c r="D16" s="4">
+        <v>600000</v>
+      </c>
+      <c r="E16" s="1">
+        <v>8</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="9">
+        <v>45388</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1">
+        <v>5</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="E17" s="1">
+        <v>8</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="9">
+        <v>45389</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="4">
+        <v>800000</v>
+      </c>
+      <c r="E18" s="1">
+        <v>7</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -970,13 +1176,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -553,7 +553,7 @@
     </row>
     <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
-        <v>44997</v>
+        <v>45058</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
-        <v>45383</v>
+        <v>45047</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="4" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
-        <v>45021</v>
+        <v>45051</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>11</v>
@@ -622,7 +622,7 @@
     </row>
     <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
-        <v>45031</v>
+        <v>45061</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>7</v>
@@ -645,7 +645,7 @@
     </row>
     <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
-        <v>45470</v>
+        <v>45073</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>8</v>
@@ -691,7 +691,7 @@
     </row>
     <row r="8" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
-        <v>45003</v>
+        <v>45064</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>6</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
-        <v>45455</v>
+        <v>45057</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -760,7 +760,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
-        <v>45603</v>
+        <v>45053</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -783,7 +783,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
-        <v>45634</v>
+        <v>45054</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
-        <v>45032</v>
+        <v>45062</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>6</v>
@@ -829,7 +829,7 @@
     </row>
     <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
-        <v>44999</v>
+        <v>45060</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>6</v>
@@ -852,7 +852,7 @@
     </row>
     <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
-        <v>45387</v>
+        <v>45051</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>10</v>
@@ -875,7 +875,7 @@
     </row>
     <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
-        <v>45389</v>
+        <v>45053</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>10</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
-        <v>45388</v>
+        <v>45052</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>6</v>
@@ -921,7 +921,7 @@
     </row>
     <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
-        <v>45389</v>
+        <v>45053</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>6</v>
